--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="282">
   <si>
     <t>TC ID</t>
   </si>
@@ -766,22 +766,100 @@
     <t>6. Reload, reselect the year and Austin, read week 1 - Save is never clicked after the import</t>
   </si>
   <si>
+    <t>TC-DSM-RWP-025</t>
+  </si>
+  <si>
+    <t>Changing Country re-scopes the weekly grid and switching back restores it</t>
+  </si>
+  <si>
+    <t>The Region Weekly Peaks tab is open and finished loading for office 1604 with the resting criteria (United States / USD / Standard). No save is involved - a criteria selection is a view switch, never an edit</t>
+  </si>
+  <si>
+    <t>1. With the tab loaded, note the selected year, region and week 1's ticks</t>
+  </si>
+  <si>
+    <t>The newest year and `Atlanta` are selected; week 1 carries its saved classification</t>
+  </si>
+  <si>
+    <t>2. In the bar above the tabs, change Country to Canada</t>
+  </si>
+  <si>
+    <t>The page stays on this tab; Currency follows the country on its own, reading `CAD`</t>
+  </si>
+  <si>
+    <t>3. Read the tab's Region selector</t>
+  </si>
+  <si>
+    <t>It now rests on a Canadian region — `Atlanta` is no longer the selection: the whole tab re-scoped to the new country</t>
+  </si>
+  <si>
+    <t>4. Read the bar's Save</t>
+  </si>
+  <si>
+    <t>Still disabled — choosing a country is navigation, not a pending change</t>
+  </si>
+  <si>
+    <t>5. Change Country back to United States</t>
+  </si>
+  <si>
+    <t>Currency returns to `USD`; the tab returns to the newest year and `Atlanta`, showing 52 week rows with week 1's ticks exactly as noted in step 1</t>
+  </si>
+  <si>
+    <t>TC-DSM-RWP-026</t>
+  </si>
+  <si>
+    <t>The threshold saves from this tab, independent of the tab's own Save</t>
+  </si>
+  <si>
+    <t>The Region Weekly Peaks tab is open and finished loading for office 1604. Data changes on office 1604 are authorized; the case restores the prior threshold through a verified save before it ends</t>
+  </si>
+  <si>
+    <t>1. With the tab loaded, note the threshold, then type a different in-range value and leave the field</t>
+  </si>
+  <si>
+    <t>The bar's Save enables</t>
+  </si>
+  <si>
+    <t>2. Read the tab's own Save inside the panel</t>
+  </si>
+  <si>
+    <t>Still disabled — an edit in the bar never marks the weekly grid dirty: the two Saves are independent</t>
+  </si>
+  <si>
+    <t>3. Switch to Company Matrix and back to Region Weekly Peaks</t>
+  </si>
+  <si>
+    <t>No warning appears, the typed value survives the round trip, and the bar's Save is still enabled</t>
+  </si>
+  <si>
+    <t>4. Click the bar's Save while this tab is open, then reload the page</t>
+  </si>
+  <si>
+    <t>The typed value is what the page shows after reload — the save committed from this tab</t>
+  </si>
+  <si>
+    <t>5. Restore the noted threshold with another save and reload</t>
+  </si>
+  <si>
+    <t>The original value is back</t>
+  </si>
+  <si>
     <t>SUMMARY</t>
   </si>
   <si>
     <t>Discount Matrix — Region Weekly Peaks</t>
   </si>
   <si>
-    <t>Automated: 24 / Pending: 0</t>
-  </si>
-  <si>
-    <t>Pass:24 Fail:0 Skipped:0 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-08-27</t>
-  </si>
-  <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>Automated: 26 / Pending: 0</t>
+  </si>
+  <si>
+    <t>Pass:26 Fail:0 Skipped:0 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-28</t>
+  </si>
+  <si>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>
@@ -1170,11 +1248,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="74" customWidth="1"/>
+    <col min="2" max="2" width="75" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
@@ -5121,45 +5199,455 @@
         <v>25</v>
       </c>
     </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>250</v>
+      </c>
+      <c r="B97" t="s">
+        <v>251</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s">
+        <v>252</v>
+      </c>
+      <c r="K97" t="s">
+        <v>253</v>
+      </c>
+      <c r="L97" t="s">
+        <v>254</v>
+      </c>
+      <c r="M97" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>254</v>
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" t="s">
+        <v>25</v>
+      </c>
+      <c r="G98" t="s">
+        <v>25</v>
+      </c>
+      <c r="H98" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" t="s">
+        <v>25</v>
+      </c>
+      <c r="K98" t="s">
+        <v>255</v>
+      </c>
+      <c r="L98" t="s">
+        <v>256</v>
+      </c>
+      <c r="M98" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" t="s">
+        <v>25</v>
+      </c>
+      <c r="G99" t="s">
+        <v>25</v>
+      </c>
+      <c r="H99" t="s">
+        <v>25</v>
+      </c>
+      <c r="I99" t="s">
+        <v>25</v>
+      </c>
+      <c r="J99" t="s">
+        <v>25</v>
+      </c>
+      <c r="K99" t="s">
+        <v>257</v>
+      </c>
+      <c r="L99" t="s">
+        <v>258</v>
+      </c>
+      <c r="M99" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" t="s">
+        <v>25</v>
+      </c>
+      <c r="H100" t="s">
+        <v>25</v>
+      </c>
+      <c r="I100" t="s">
+        <v>25</v>
+      </c>
+      <c r="J100" t="s">
+        <v>25</v>
+      </c>
+      <c r="K100" t="s">
+        <v>259</v>
+      </c>
+      <c r="L100" t="s">
+        <v>260</v>
+      </c>
+      <c r="M100" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" t="s">
+        <v>25</v>
+      </c>
+      <c r="E101" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" t="s">
+        <v>25</v>
+      </c>
+      <c r="G101" t="s">
+        <v>25</v>
+      </c>
+      <c r="H101" t="s">
+        <v>25</v>
+      </c>
+      <c r="I101" t="s">
+        <v>25</v>
+      </c>
+      <c r="J101" t="s">
+        <v>25</v>
+      </c>
+      <c r="K101" t="s">
+        <v>261</v>
+      </c>
+      <c r="L101" t="s">
+        <v>262</v>
+      </c>
+      <c r="M101" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>263</v>
+      </c>
+      <c r="B102" t="s">
+        <v>264</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>20</v>
+      </c>
+      <c r="I102" t="s">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s">
+        <v>265</v>
+      </c>
+      <c r="K102" t="s">
+        <v>266</v>
+      </c>
+      <c r="L102" t="s">
+        <v>267</v>
+      </c>
+      <c r="M102" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" t="s">
+        <v>25</v>
+      </c>
+      <c r="H103" t="s">
+        <v>25</v>
+      </c>
+      <c r="I103" t="s">
+        <v>25</v>
+      </c>
+      <c r="J103" t="s">
+        <v>25</v>
+      </c>
+      <c r="K103" t="s">
+        <v>268</v>
+      </c>
+      <c r="L103" t="s">
+        <v>269</v>
+      </c>
+      <c r="M103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" t="s">
+        <v>25</v>
+      </c>
+      <c r="H104" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104" t="s">
+        <v>25</v>
+      </c>
+      <c r="J104" t="s">
+        <v>25</v>
+      </c>
+      <c r="K104" t="s">
+        <v>270</v>
+      </c>
+      <c r="L104" t="s">
+        <v>271</v>
+      </c>
+      <c r="M104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" t="s">
+        <v>25</v>
+      </c>
+      <c r="E105" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" t="s">
+        <v>25</v>
+      </c>
+      <c r="H105" t="s">
+        <v>25</v>
+      </c>
+      <c r="I105" t="s">
+        <v>25</v>
+      </c>
+      <c r="J105" t="s">
+        <v>25</v>
+      </c>
+      <c r="K105" t="s">
+        <v>272</v>
+      </c>
+      <c r="L105" t="s">
+        <v>273</v>
+      </c>
+      <c r="M105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" t="s">
+        <v>25</v>
+      </c>
+      <c r="H106" t="s">
+        <v>25</v>
+      </c>
+      <c r="I106" t="s">
+        <v>25</v>
+      </c>
+      <c r="J106" t="s">
+        <v>25</v>
+      </c>
+      <c r="K106" t="s">
+        <v>274</v>
+      </c>
+      <c r="L106" t="s">
+        <v>275</v>
+      </c>
+      <c r="M106" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5175,7 +5663,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -859,7 +859,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -859,7 +859,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -859,7 +859,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -859,7 +859,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -859,7 +859,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -859,7 +859,7 @@
     <t>Last Updated: 2026-08-28</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
+++ b/clients/encore/testcases/discount-matrix/discount-matrix-region-weekly-peaks.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="discount_matrix_region_peaks" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="281">
   <si>
     <t>TC ID</t>
   </si>
@@ -857,9 +856,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-28</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -5654,20 +5650,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>